--- a/output/stock_quant_scores/META_info.xlsx
+++ b/output/stock_quant_scores/META_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FT2"/>
+  <dimension ref="A1:FX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,240 +1066,260 @@
       </c>
       <c r="DY1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>ipoExpectedDate</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>ipoExpectedDate</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1420,28 +1440,28 @@
         <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>755.4</v>
+        <v>748.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>757.953</v>
+        <v>750</v>
       </c>
       <c r="AD2" t="n">
-        <v>752.5251</v>
+        <v>737.3532</v>
       </c>
       <c r="AE2" t="n">
-        <v>760.49</v>
+        <v>751.9299</v>
       </c>
       <c r="AF2" t="n">
-        <v>755.4</v>
+        <v>748.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>757.9527</v>
+        <v>750</v>
       </c>
       <c r="AH2" t="n">
-        <v>752.5251</v>
+        <v>737.3532</v>
       </c>
       <c r="AI2" t="n">
-        <v>760.49</v>
+        <v>751.9299</v>
       </c>
       <c r="AJ2" t="n">
         <v>2.1</v>
@@ -1459,31 +1479,31 @@
         <v>1.242</v>
       </c>
       <c r="AO2" t="n">
-        <v>27.470621</v>
+        <v>26.957232</v>
       </c>
       <c r="AP2" t="n">
-        <v>29.935375</v>
+        <v>29.397234</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5613161</v>
+        <v>9617450</v>
       </c>
       <c r="AR2" t="n">
-        <v>5611417</v>
+        <v>9617450</v>
       </c>
       <c r="AS2" t="n">
-        <v>11665342</v>
+        <v>11459931</v>
       </c>
       <c r="AT2" t="n">
-        <v>11758280</v>
+        <v>11805260</v>
       </c>
       <c r="AU2" t="n">
-        <v>11758280</v>
+        <v>11805260</v>
       </c>
       <c r="AV2" t="n">
-        <v>757.24</v>
+        <v>743.4299999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>796.17</v>
+        <v>744.09</v>
       </c>
       <c r="AX2" t="n">
         <v>1</v>
@@ -1492,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1902608121856</v>
+        <v>1868405276672</v>
       </c>
       <c r="BA2" t="n">
         <v>479.8</v>
@@ -1507,19 +1527,19 @@
         <v>17.55</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.642643</v>
+        <v>10.44946</v>
       </c>
       <c r="BF2" t="n">
-        <v>748.2754</v>
+        <v>751.0476</v>
       </c>
       <c r="BG2" t="n">
-        <v>662.4834</v>
+        <v>664.5176</v>
       </c>
       <c r="BH2" t="n">
         <v>2.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.002713794</v>
+        <v>0.0027373116</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -1530,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1900160614400</v>
+        <v>1870894202880</v>
       </c>
       <c r="BM2" t="n">
         <v>0.39992002</v>
@@ -1542,40 +1562,40 @@
         <v>2168962480</v>
       </c>
       <c r="BP2" t="n">
-        <v>24374357</v>
+        <v>26292755</v>
       </c>
       <c r="BQ2" t="n">
-        <v>25056459</v>
+        <v>27725780</v>
       </c>
       <c r="BR2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0097</v>
+        <v>0.0105</v>
       </c>
       <c r="BU2" t="n">
         <v>0.00079</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.79789</v>
+        <v>0.7984</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.93</v>
+        <v>2.58</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0112</v>
+        <v>0.0121</v>
       </c>
       <c r="BY2" t="n">
-        <v>2512141475</v>
+        <v>2551555640</v>
       </c>
       <c r="BZ2" t="n">
         <v>77.532</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.768418</v>
+        <v>9.5928135</v>
       </c>
       <c r="CB2" t="n">
         <v>1735603200</v>
@@ -1593,22 +1613,22 @@
         <v>71507001344</v>
       </c>
       <c r="CG2" t="n">
-        <v>27.57</v>
+        <v>27.59</v>
       </c>
       <c r="CH2" t="n">
         <v>25.3</v>
       </c>
       <c r="CI2" t="n">
-        <v>10.627</v>
+        <v>10.463</v>
       </c>
       <c r="CJ2" t="n">
-        <v>20.154</v>
+        <v>19.844</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.32920408</v>
+        <v>0.29926276</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CM2" t="n">
         <v>0.525</v>
@@ -1622,7 +1642,7 @@
         </is>
       </c>
       <c r="CP2" t="n">
-        <v>757.5</v>
+        <v>743.75</v>
       </c>
       <c r="CQ2" t="n">
         <v>1086</v>
@@ -1744,177 +1764,189 @@
       </c>
       <c r="DY2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DZ2" t="n">
-        <v>1758740010</v>
-      </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EB2" t="n">
+        <v>1758931198</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1758916800</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>27.96433</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>26.596382</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-7.2976074</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.009716571</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>79.23242</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0.119233</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>1.4 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="EQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="inlineStr">
         <is>
           <t>NMS</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>finmb_20765463</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EU2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="EE2" t="n">
+      <c r="EV2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="EG2" t="b">
+      <c r="EX2" t="b">
         <v>0</v>
       </c>
-      <c r="EH2" t="n">
-        <v>0.26012254</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>757.365</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>27.96433</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>27.083252</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>9.089600000000001</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.012147399</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>94.88159</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.14322108</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>2022-06-09</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>1.4 - Strong Buy</t>
-        </is>
-      </c>
-      <c r="EW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EX2" t="b">
+      <c r="EY2" t="n">
+        <v>-0.688998</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>743.75</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>-0.034959298</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>743.49</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>-0.26000977</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>-5.15997</v>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>737.3532 - 751.9299</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="FG2" t="n">
+        <v>11459931</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>263.95</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>0.5501250600000001</v>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>479.8 - 796.25</t>
+        </is>
+      </c>
+      <c r="FK2" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>-0.06593407</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>29.926277</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>1759104000</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1753905600</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>1761768000</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>1761768000</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>1753909200</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>1753909200</v>
+      </c>
+      <c r="FT2" t="b">
         <v>1</v>
       </c>
-      <c r="EY2" t="n">
+      <c r="FU2" t="n">
         <v>1337347800000</v>
       </c>
-      <c r="EZ2" t="n">
-        <v>1.9649658</v>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>752.5251 - 760.49</t>
-        </is>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="FC2" t="n">
-        <v>11665342</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>277.565</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>0.57850146</v>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>479.8 - 796.25</t>
-        </is>
-      </c>
-      <c r="FG2" t="n">
-        <v>-38.88501</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>-0.048835177</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>32.92041</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>1759104000</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>1753905600</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>1761768000</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>1761768000</v>
-      </c>
-      <c r="FN2" t="n">
-        <v>1753909200</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>1753909200</v>
-      </c>
-      <c r="FP2" t="b">
+      <c r="FV2" t="b">
         <v>1</v>
       </c>
-      <c r="FQ2" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="FR2" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="FS2" t="inlineStr">
+      <c r="FW2" t="inlineStr">
         <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="FT2" t="n">
-        <v>2.0623</v>
+      <c r="FX2" t="n">
+        <v>2.0305</v>
       </c>
     </row>
   </sheetData>
